--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9591836734693877</v>
+        <v>0.9489795918367347</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7642857142857142</v>
+        <v>0.7112676056338029</v>
       </c>
       <c r="D2">
-        <v>0.2598425196850394</v>
+        <v>0.3059701492537313</v>
       </c>
       <c r="E2">
         <v>98</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
